--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -439,110 +439,255 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>record_kind</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>country_code</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>country_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>disease_id</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>disease_name_en</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>disease_name_zh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>year_month</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>cases</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>weekly_equiv_cases</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>incidence_rate_per_100k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>incidence_rate_source</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mortality_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>series_code</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>source_series_code</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>source_label</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>metric_type</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>reporting_basis</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>temporal_granularity</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>geography_key</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>dimension_key</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>mapping_relation</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>comparability</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>aggregation_policy</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>availability_status</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>missing_value_policy</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>definition_version</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>case_definition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>case_definition_uri</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>quality_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_selected_series</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>data_layer</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>projection_policy</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>coverage_status</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>loss_risk</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>selected_series_codes</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>available_series_count</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>provenance_note</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
         <is>
           <t>primary_source_scope</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>primary_source_label</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>primary_source_url</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>primary_source_type</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>source_scopes</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>source_labels</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>source_urls</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>source_types</t>
         </is>
@@ -571,99 +716,139 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>76</v>
-      </c>
       <c r="N2" t="n">
-        <v>17.16129032258064</v>
+        <v>171</v>
       </c>
       <c r="O2" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.43735795451859</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>web</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -690,99 +875,214 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>54</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>12.19354838709677</v>
+        <v>171</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.021280651894788</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
+        <v>171</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -809,99 +1109,142 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>55</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>13.75</v>
+        <v>24</v>
       </c>
       <c r="O4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.040193256559506</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>0.4245541981909216</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>web</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -928,99 +1271,214 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>45</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>10.16129032258065</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.8510672099123231</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
+        <v>24</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>case_notifications</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1047,97 +1505,126 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>48</v>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>11.2</v>
+        <v>76</v>
       </c>
       <c r="O6" t="n">
+        <v>76</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" t="n">
-        <v>0.9078050239064779</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>1.43735795451859</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -1166,99 +1653,7836 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>69</v>
+      </c>
+      <c r="O7" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.6447967495515509</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>69</v>
+      </c>
+      <c r="O8" t="n">
+        <v>69</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>154</v>
+      </c>
+      <c r="O9" t="n">
+        <v>154</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>154</v>
+      </c>
+      <c r="O10" t="n">
+        <v>154</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3891746816750113</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>22</v>
+      </c>
+      <c r="O12" t="n">
+        <v>22</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>NZ</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>D157</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>侵袭性A族链球菌感染</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>54</v>
+      </c>
+      <c r="O13" t="n">
+        <v>54</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.021280651894788</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>59</v>
+      </c>
+      <c r="O14" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5513479452687174</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>59</v>
+      </c>
+      <c r="O15" t="n">
+        <v>59</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>150</v>
+      </c>
+      <c r="O16" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>150</v>
+      </c>
+      <c r="O17" t="n">
+        <v>150</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>31</v>
+      </c>
+      <c r="O18" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.548382505996607</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>31</v>
+      </c>
+      <c r="O19" t="n">
+        <v>31</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>55</v>
+      </c>
+      <c r="O20" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.040193256559506</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>57</v>
+      </c>
+      <c r="O21" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5326581844121507</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>57</v>
+      </c>
+      <c r="O22" t="n">
+        <v>57</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>127</v>
+      </c>
+      <c r="O23" t="n">
+        <v>127</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>127</v>
+      </c>
+      <c r="O24" t="n">
+        <v>127</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>14</v>
+      </c>
+      <c r="O25" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.2476566156113709</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>14</v>
+      </c>
+      <c r="O26" t="n">
+        <v>14</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>45</v>
+      </c>
+      <c r="O27" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.8510672099123231</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>41</v>
+      </c>
+      <c r="O28" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.3831400975596171</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>41</v>
+      </c>
+      <c r="O29" t="n">
+        <v>41</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>129</v>
+      </c>
+      <c r="O30" t="n">
+        <v>129</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CA-ON</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ontario, Canada</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>129</v>
+      </c>
+      <c r="O31" t="n">
+        <v>129</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>pho_idto_monthly</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Public Health Ontario IDTO Monthly</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>27</v>
+      </c>
+      <c r="O32" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.4776234729647867</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>27</v>
+      </c>
+      <c r="O33" t="n">
+        <v>27</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>48</v>
+      </c>
+      <c r="O34" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.9078050239064779</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr"/>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>phf_monthly</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>32</v>
+      </c>
+      <c r="O35" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.2990361737050671</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>32</v>
+      </c>
+      <c r="O36" t="n">
+        <v>32</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N37" t="n">
+        <v>15</v>
+      </c>
+      <c r="O37" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.2653463738693259</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>15</v>
+      </c>
+      <c r="O38" t="n">
+        <v>15</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NZ</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
         <v>48</v>
       </c>
-      <c r="N7" t="n">
-        <v>10.83870967741935</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="O39" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R39" t="n">
         <v>0.9078050239064779</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://www.phfscience.nz/digital-library/</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>phf_monthly</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
         <is>
           <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="BC39" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>phf_monthly</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>web</t>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>50</v>
+      </c>
+      <c r="O40" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.4672440214141673</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>50</v>
+      </c>
+      <c r="O41" t="n">
+        <v>50</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>17</v>
+      </c>
+      <c r="O42" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.3007258903852361</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>17</v>
+      </c>
+      <c r="O43" t="n">
+        <v>17</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>35</v>
+      </c>
+      <c r="O44" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.3270708149899171</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>35</v>
+      </c>
+      <c r="O45" t="n">
+        <v>35</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -1295,7 +9519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -1374,62 +9598,104 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>record_count</t>
+          <t>projection_record_count</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schema_version</t>
+          <t>record_count</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>total_cases</t>
+          <t>schema_version</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>326</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>total_deaths</t>
+          <t>source_observation_count</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>window_end</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2029-12-31</t>
-        </is>
+          <t>source_series_count</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>total_basis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>total_cases</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>total_deaths</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>window_start</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -1565,28 +1565,42 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1653,17 +1667,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1697,25 +1711,39 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="O7" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.6447967495515509</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>76</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1723,6 +1751,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN7" t="b">
+        <v>1</v>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -1740,7 +1826,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
@@ -1753,42 +1839,42 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1901,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1864,98 +1950,26 @@
       <c r="O8" t="n">
         <v>69</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6447967495515509</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN8" t="b">
-        <v>1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -2049,17 +2063,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2084,31 +2098,48 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>154</v>
+        <v>69</v>
       </c>
       <c r="O9" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>69</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -2116,6 +2147,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN9" t="b">
+        <v>1</v>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2133,7 +2222,7 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT9" t="n">
@@ -2146,42 +2235,42 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2297,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2257,98 +2346,23 @@
       <c r="O10" t="n">
         <v>154</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Group A Streptococcal Disease, Invasive</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN10" t="b">
-        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2442,17 +2456,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2486,25 +2500,39 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>154</v>
       </c>
       <c r="O11" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3891746816750113</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>154</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2512,6 +2540,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN11" t="b">
+        <v>1</v>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -2529,7 +2615,7 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT11" t="n">
@@ -2542,42 +2628,42 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2690,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2653,98 +2739,26 @@
       <c r="O12" t="n">
         <v>22</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3891746816750113</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Syst. gr. A streptokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN12" t="b">
-        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -2838,17 +2852,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2882,84 +2896,170 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>54</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.021280651894788</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN13" t="b">
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -2991,12 +3091,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3030,16 +3130,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O14" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5513479452687174</v>
+        <v>1.021280651894788</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3048,7 +3148,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -3073,7 +3173,7 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -3086,42 +3186,42 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3253,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3192,29 +3292,29 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="O15" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3224,7 +3324,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -3239,7 +3339,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -3274,17 +3374,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3307,7 +3407,7 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT15" t="n">
@@ -3320,42 +3420,42 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3487,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3417,31 +3517,34 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="O16" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="R16" t="n">
+        <v>0.5513479452687174</v>
+      </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -3466,7 +3569,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -3479,42 +3582,42 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -3546,12 +3649,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3576,38 +3679,38 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="O17" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Group A Streptococcal Disease, Invasive</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -3617,7 +3720,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -3632,7 +3735,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3667,17 +3770,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -3700,7 +3803,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -3713,42 +3816,42 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3883,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3819,25 +3922,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="O18" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>0.548382505996607</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3862,7 +3962,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -3875,42 +3975,42 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -3942,12 +4042,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3981,29 +4081,29 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="O19" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -4013,7 +4113,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -4028,7 +4128,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -4063,17 +4163,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4096,7 +4196,7 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
@@ -4109,42 +4209,42 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -4176,12 +4276,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4215,84 +4315,98 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="O20" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.040193256559506</v>
+        <v>0.548382505996607</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -4319,17 +4433,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4363,25 +4477,39 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="O21" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.5326581844121507</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>31</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -4389,6 +4517,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN21" t="b">
+        <v>1</v>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4406,7 +4592,7 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT21" t="n">
@@ -4419,42 +4605,42 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -4481,17 +4667,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -4525,39 +4711,25 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="O22" t="n">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.040193256559506</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -4565,64 +4737,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN22" t="b">
-        <v>1</v>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4640,7 +4754,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT22" t="n">
@@ -4653,42 +4767,42 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4715,17 +4829,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4750,31 +4864,48 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="O23" t="n">
-        <v>127</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
+        <v>55</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -4782,6 +4913,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN23" t="b">
+        <v>1</v>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -4799,7 +4988,7 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT23" t="n">
@@ -4812,42 +5001,42 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -4874,17 +5063,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -4909,48 +5098,34 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="O24" t="n">
-        <v>127</v>
+        <v>57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.5326581844121507</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Group A Streptococcal Disease, Invasive</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -4958,64 +5133,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN24" t="b">
-        <v>1</v>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5033,7 +5150,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT24" t="n">
@@ -5046,42 +5163,42 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -5108,17 +5225,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5143,34 +5260,48 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="N25" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="O25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.2476566156113709</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>57</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -5178,6 +5309,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN25" t="b">
+        <v>1</v>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5195,7 +5384,7 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT25" t="n">
@@ -5208,42 +5397,42 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -5270,17 +5459,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5314,39 +5503,22 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>127</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Syst. gr. A streptokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -5354,64 +5526,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN26" t="b">
-        <v>1</v>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -5429,7 +5543,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT26" t="n">
@@ -5442,42 +5556,42 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5504,17 +5618,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -5548,84 +5662,170 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="O27" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.8510672099123231</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>127</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN27" t="b">
+        <v>1</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS27" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -5657,12 +5857,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -5696,16 +5896,16 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="O28" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3831400975596171</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -5714,7 +5914,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -5739,7 +5939,7 @@
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
@@ -5752,42 +5952,42 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -5819,12 +6019,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5858,29 +6058,29 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="O29" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -5905,7 +6105,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -5940,17 +6140,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -5973,7 +6173,7 @@
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
@@ -5986,42 +6186,42 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6253,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6083,31 +6283,34 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="O30" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
+      <c r="R30" t="n">
+        <v>0.8510672099123231</v>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -6132,7 +6335,7 @@
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT30" t="n">
@@ -6145,42 +6348,42 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6415,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6242,38 +6445,38 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Group A Streptococcal Disease, Invasive</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -6298,7 +6501,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -6333,17 +6536,17 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6366,7 +6569,7 @@
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT31" t="n">
@@ -6379,42 +6582,42 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6446,12 +6649,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6476,25 +6679,25 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O32" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4776234729647867</v>
+        <v>0.3831400975596171</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6503,7 +6706,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -6528,7 +6731,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -6541,42 +6744,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6608,12 +6811,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6638,38 +6841,38 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="O33" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -6694,7 +6897,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6729,17 +6932,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6762,7 +6965,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6775,42 +6978,42 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6842,12 +7045,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6881,84 +7084,95 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="O34" t="n">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
-      <c r="R34" t="n">
-        <v>0.9078050239064779</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS34" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -6985,17 +7199,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -7029,25 +7243,39 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="O35" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.2990361737050671</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>129</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Group A Streptococcal Disease, Invasive</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -7055,6 +7283,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7072,7 +7358,7 @@
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT35" t="n">
@@ -7085,42 +7371,42 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -7147,17 +7433,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -7191,39 +7477,25 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="O36" t="n">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.4776234729647867</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -7231,64 +7503,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN36" t="b">
-        <v>1</v>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7306,7 +7520,7 @@
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT36" t="n">
@@ -7319,42 +7533,42 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7595,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7416,40 +7630,112 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="O37" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.2653463738693259</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>27</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -7543,17 +7829,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -7578,48 +7864,34 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>48</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.9078050239064779</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>Syst. gr. A streptokokksykdom</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -7627,64 +7899,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN38" t="b">
-        <v>1</v>
-      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -7702,7 +7916,7 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
@@ -7715,42 +7929,42 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7991,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7812,12 +8026,12 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N39" t="n">
@@ -7826,39 +8040,125 @@
       <c r="O39" t="n">
         <v>48</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0.9078050239064779</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7960,25 +8260,25 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.4672440214141673</v>
+        <v>0.2990361737050671</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -8122,19 +8422,19 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="O41" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8356,25 +8656,25 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O42" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.2653463738693259</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8518,19 +8818,19 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O43" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -8722,12 +9022,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -8752,25 +9052,25 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N44" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="O44" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3270708149899171</v>
+        <v>0.9078050239064779</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -8779,7 +9079,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -8804,7 +9104,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -8817,42 +9117,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8884,12 +9184,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -8914,38 +9214,38 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N45" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="O45" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -8955,7 +9255,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -8970,7 +9270,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -9005,17 +9305,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9038,7 +9338,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -9051,42 +9351,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9118,12 +9418,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -9148,25 +9448,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.4672440214141673</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9175,7 +9475,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -9200,7 +9500,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -9213,42 +9513,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9280,12 +9580,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -9310,38 +9610,38 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -9366,7 +9666,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -9401,17 +9701,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9434,7 +9734,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -9447,40 +9747,1228 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>17</v>
+      </c>
+      <c r="O48" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.3007258903852361</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV48" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW47" t="inlineStr">
+      <c r="AW48" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr">
+      <c r="AY48" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA47" t="inlineStr">
+      <c r="BA48" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB47" t="inlineStr">
+      <c r="BB48" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC47" t="inlineStr">
+      <c r="BC48" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>17</v>
+      </c>
+      <c r="O49" t="n">
+        <v>17</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>35</v>
+      </c>
+      <c r="O50" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.3270708149899171</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>35</v>
+      </c>
+      <c r="O51" t="n">
+        <v>35</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
+        </is>
+      </c>
+      <c r="AT51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -9612,7 +11100,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -9632,7 +11120,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -9642,7 +11130,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>171</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>24</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4245541981909216</v>
       </c>
@@ -1803,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -1950,9 +1944,6 @@
       <c r="O8" t="n">
         <v>69</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.6447967495515509</v>
       </c>
@@ -2346,9 +2337,6 @@
       <c r="O10" t="n">
         <v>154</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2739,9 +2727,6 @@
       <c r="O12" t="n">
         <v>22</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.3891746816750113</v>
       </c>
@@ -3384,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3531,9 +3516,6 @@
       <c r="O16" t="n">
         <v>59</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.5513479452687174</v>
       </c>
@@ -3927,9 +3909,6 @@
       <c r="O18" t="n">
         <v>150</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4320,9 +4299,6 @@
       <c r="O20" t="n">
         <v>31</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.548382505996607</v>
       </c>
@@ -4965,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5112,9 +5088,6 @@
       <c r="O24" t="n">
         <v>57</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.5326581844121507</v>
       </c>
@@ -5508,9 +5481,6 @@
       <c r="O26" t="n">
         <v>127</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5901,9 +5871,6 @@
       <c r="O28" t="n">
         <v>14</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.2476566156113709</v>
       </c>
@@ -6297,9 +6264,6 @@
       <c r="O30" t="n">
         <v>45</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.8510672099123231</v>
       </c>
@@ -6546,7 +6510,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6693,9 +6657,6 @@
       <c r="O32" t="n">
         <v>41</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.3831400975596171</v>
       </c>
@@ -7089,9 +7050,6 @@
       <c r="O34" t="n">
         <v>129</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7482,9 +7440,6 @@
       <c r="O36" t="n">
         <v>27</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.4776234729647867</v>
       </c>
@@ -7878,9 +7833,6 @@
       <c r="O38" t="n">
         <v>48</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -8127,7 +8079,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8274,9 +8226,6 @@
       <c r="O40" t="n">
         <v>32</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.2990361737050671</v>
       </c>
@@ -8665,16 +8614,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O42" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R42" t="n">
-        <v>0.2653463738693259</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8827,10 +8773,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -9066,9 +9012,6 @@
       <c r="O44" t="n">
         <v>48</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.9078050239064779</v>
       </c>
@@ -9315,7 +9258,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9462,9 +9405,6 @@
       <c r="O46" t="n">
         <v>50</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.4672440214141673</v>
       </c>
@@ -9858,9 +9798,6 @@
       <c r="O48" t="n">
         <v>17</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.3007258903852361</v>
       </c>
@@ -10254,9 +10191,6 @@
       <c r="O50" t="n">
         <v>35</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.3270708149899171</v>
       </c>
@@ -10645,16 +10579,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10807,10 +10738,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
@@ -11152,7 +11083,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1550</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2488,10 +2488,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O11" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3904,10 +3904,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O18" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O19" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O34" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O35" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8614,22 +8614,19 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="O42" t="n">
-        <v>16</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.283036132127281</v>
+        <v>108</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -8654,7 +8651,7 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT42" t="n">
@@ -8667,42 +8664,42 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8734,12 +8731,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -8773,29 +8770,29 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="O43" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Group A Streptococcal Disease, Invasive</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -8805,7 +8802,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -8820,7 +8817,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -8855,17 +8852,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Ontario IDTO current-year preliminary invasive group A streptococcal disease notifications.</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -8888,7 +8885,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_INVASIVE_GROUP_A_STREPTOCOCCAL_DISEASE_MONTHLY</t>
         </is>
       </c>
       <c r="AT43" t="n">
@@ -8901,42 +8898,42 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -8968,12 +8965,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -9007,13 +9004,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="R44" t="n">
-        <v>0.9078050239064779</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9022,7 +9019,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -9047,7 +9044,7 @@
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
@@ -9060,42 +9057,42 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -9127,12 +9124,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -9166,29 +9163,29 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Invasive group A streptococcal infection</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -9198,7 +9195,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -9213,7 +9210,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -9248,17 +9245,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9281,7 +9278,7 @@
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
@@ -9294,42 +9291,42 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -9361,12 +9358,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -9400,13 +9397,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O46" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4672440214141673</v>
+        <v>0.9078050239064779</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9415,7 +9412,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -9440,7 +9437,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -9453,42 +9450,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9520,12 +9517,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -9559,29 +9556,29 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O47" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -9591,7 +9588,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -9606,7 +9603,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -9641,17 +9638,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9674,7 +9671,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -9687,42 +9684,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9754,12 +9751,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9784,22 +9781,22 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="O48" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3007258903852361</v>
+        <v>0.4672440214141673</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9808,7 +9805,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -9833,7 +9830,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT48" t="n">
@@ -9846,42 +9843,42 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9910,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -9943,38 +9940,38 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="O49" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -9999,7 +9996,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -10034,17 +10031,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10067,7 +10064,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT49" t="n">
@@ -10080,42 +10077,42 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -10147,12 +10144,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10186,13 +10183,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="O50" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="R50" t="n">
-        <v>0.3270708149899171</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10201,7 +10198,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -10226,7 +10223,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -10239,42 +10236,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10306,12 +10303,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10345,29 +10342,29 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="O51" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Syst. gr. A streptokokksykdom</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -10392,7 +10389,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -10427,17 +10424,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10460,7 +10457,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NO_FHI_709_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -10473,42 +10470,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10540,12 +10537,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10570,22 +10567,22 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.3270708149899171</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10594,7 +10591,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10619,7 +10616,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10632,42 +10629,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10696,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10729,38 +10726,38 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10785,7 +10782,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10820,17 +10817,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10853,7 +10850,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10866,40 +10863,433 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>8</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.1415180660636405</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW53" t="inlineStr">
+      <c r="AW54" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
+      <c r="AX54" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY53" t="inlineStr">
+      <c r="AY54" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA53" t="inlineStr">
+      <c r="BA54" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB53" t="inlineStr">
+      <c r="BB54" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC53" t="inlineStr">
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>8</v>
+      </c>
+      <c r="O55" t="n">
+        <v>8</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -11021,7 +11411,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -11031,7 +11421,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -11051,7 +11441,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -11083,7 +11473,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1559</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -9790,13 +9790,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4672440214141673</v>
+        <v>0.457899140985884</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9949,10 +9949,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -10969,13 +10969,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R54" t="n">
-        <v>0.1415180660636405</v>
+        <v>0.2476566156113709</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1672</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -10537,12 +10537,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10576,13 +10576,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O52" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="R52" t="n">
-        <v>0.3270708149899171</v>
+        <v>1.134756279883097</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10629,42 +10629,42 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10735,29 +10735,29 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="O53" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
+          <t>Invasive group A streptococcal infection</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10817,17 +10817,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
+          <t>New Zealand PHF Science monthly invasive group A streptococcal infection notifications.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10850,7 +10850,7 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_IGAS</t>
+          <t>SER_NZ_INVASIVE_GROUP_A_STREPTOCOCCAL_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10863,42 +10863,42 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -10930,12 +10930,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10960,22 +10960,22 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="O54" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.3270708149899171</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11022,42 +11022,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -11089,12 +11089,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11119,38 +11119,38 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="O55" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Syst. gr. A streptokokksykdom</t>
+          <t>Betahemolytiska grupp A-streptokocker (invasiv)</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11210,17 +11210,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Invasive GAS source category.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_709_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_IGAS</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11256,40 +11256,433 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>14</v>
+      </c>
+      <c r="O56" t="n">
+        <v>14</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.2476566156113709</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW55" t="inlineStr">
+      <c r="AW56" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AX56" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr">
+      <c r="AY56" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA55" t="inlineStr">
+      <c r="BA56" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB55" t="inlineStr">
+      <c r="BB56" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC55" t="inlineStr">
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>14</v>
+      </c>
+      <c r="O57" t="n">
+        <v>14</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -11411,7 +11804,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -11421,7 +11814,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -11441,7 +11834,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -11473,7 +11866,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1677</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d157/2026-2029.xlsx
+++ b/diseases/d157/2026-2029.xlsx
@@ -11362,13 +11362,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R56" t="n">
-        <v>0.2476566156113709</v>
+        <v>0.3007258903852361</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11521,10 +11521,10 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
@@ -11683,6 +11683,399 @@
         </is>
       </c>
       <c r="BC57" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>invasive-group-a-streptococcal-infection</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D157</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Invasive group A streptococcal infection</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>侵袭性A族链球菌感染</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Syst. gr. A streptokokksykdom</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS systemic group A streptococcal category.</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN59" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_709_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -11721,7 +12114,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -11804,7 +12197,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -11814,7 +12207,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -11834,7 +12227,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -11866,7 +12259,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1737</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="16">
